--- a/TestFiles/ExcelFiles/PercentOfCharge.xlsx
+++ b/TestFiles/ExcelFiles/PercentOfCharge.xlsx
@@ -74,7 +74,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>8.54</v>
+        <v>10.14</v>
       </c>
     </row>
   </sheetData>

--- a/TestFiles/ExcelFiles/PercentOfCharge.xlsx
+++ b/TestFiles/ExcelFiles/PercentOfCharge.xlsx
@@ -74,7 +74,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>12.06</v>
+        <v>6.88</v>
       </c>
     </row>
   </sheetData>
